--- a/r_test/plot_metrics/Cluster_Assignement.xlsx
+++ b/r_test/plot_metrics/Cluster_Assignement.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D355"/>
+  <dimension ref="A1:E353"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,371 +375,476 @@
           <t>Latitude</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1_FRST_AK_3</t>
+          <t>1040_AN_TJ_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C2">
-        <v>-148.71622222</v>
+        <v>-162.73186261</v>
       </c>
       <c r="D2">
-        <v>69.67408333</v>
+        <v>67.46840754999999</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2_FRST_AK_3</t>
+          <t>1041_AN_TJ_1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C3">
-        <v>-148.71716667</v>
+        <v>-162.73045967</v>
       </c>
       <c r="D3">
-        <v>69.67386111</v>
+        <v>67.46940259</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3_FRST_AK_3</t>
+          <t>1042_AN_TJ_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C4">
-        <v>-148.71733333</v>
+        <v>-162.72862475</v>
       </c>
       <c r="D4">
-        <v>69.67419443999999</v>
+        <v>67.46993353000001</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4_FRST_AK_3</t>
+          <t>1043_AN_TJ_1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C5">
-        <v>-148.71875</v>
+        <v>-162.73046769</v>
       </c>
       <c r="D5">
-        <v>69.67397222</v>
+        <v>67.47082311</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5_FRST_AK_3</t>
+          <t>1044_AN_TJ_1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C6">
-        <v>-148.72027778</v>
+        <v>-162.72827019</v>
       </c>
       <c r="D6">
-        <v>69.67444444</v>
+        <v>67.47144795</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6_FRST_AK_3</t>
+          <t>1045_AN_TJ_1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C7">
-        <v>-148.72111111</v>
+        <v>-162.72242204</v>
       </c>
       <c r="D7">
-        <v>69.67472222000001</v>
+        <v>67.4733983</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7_FRST_AK_3</t>
+          <t>1046_AN_TJ_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C8">
-        <v>-148.72111111</v>
+        <v>-162.71976654</v>
       </c>
       <c r="D8">
-        <v>69.675</v>
+        <v>67.47238161</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8_FRST_AK_3</t>
+          <t>1047_AN_TJ_1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C9">
-        <v>-148.72052778</v>
+        <v>-162.71556098</v>
       </c>
       <c r="D9">
-        <v>69.67430555999999</v>
+        <v>67.46938401</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9_FRST_AK_3</t>
+          <t>1048_AN_TJ_1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C10">
-        <v>-148.72052778</v>
+        <v>-162.71556098</v>
       </c>
       <c r="D10">
-        <v>69.67427778</v>
+        <v>67.46938401</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10_FRST_AK_3</t>
+          <t>1049_AN_TJ_1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C11">
-        <v>-148.72047222</v>
+        <v>-162.71252794</v>
       </c>
       <c r="D11">
-        <v>69.67397222</v>
+        <v>67.46938523999999</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11_FRST_AK_3</t>
+          <t>1121_AN_TJ_2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C12">
-        <v>-148.7205</v>
+        <v>-162.3071079</v>
       </c>
       <c r="D12">
-        <v>69.67427778</v>
+        <v>67.96023532</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12_FRST_AK_3</t>
+          <t>1122_AN_TJ_2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C13">
-        <v>-148.72055556</v>
+        <v>-162.30820942</v>
       </c>
       <c r="D13">
-        <v>69.67444444</v>
+        <v>67.96015801</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13_FRST_AK_3</t>
+          <t>1123_AN_TJ_2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C14">
-        <v>-148.72083333</v>
+        <v>-162.30826366</v>
       </c>
       <c r="D14">
-        <v>69.67472222000001</v>
+        <v>67.96050605000001</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14_FRST_AK_3</t>
+          <t>1124_AN_TJ_2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C15">
-        <v>-148.71716667</v>
+        <v>-162.3115999</v>
       </c>
       <c r="D15">
-        <v>69.67386111</v>
+        <v>67.95979371999999</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15_FRST_AK_3</t>
+          <t>1125_AN_TJ_2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C16">
-        <v>-148.71733333</v>
+        <v>-162.31303584</v>
       </c>
       <c r="D16">
-        <v>69.67419443999999</v>
+        <v>67.95891485999999</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17_FRST_AK_3</t>
+          <t>1126_AN_TJ_2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C17">
-        <v>-148.71875</v>
+        <v>-162.31208496</v>
       </c>
       <c r="D17">
-        <v>69.67397222</v>
+        <v>67.95923406999999</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18_FRST_AK_3</t>
+          <t>1127_AN_TJ_2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C18">
-        <v>-148.72172222</v>
+        <v>-162.30292467</v>
       </c>
       <c r="D18">
-        <v>69.67455556</v>
+        <v>67.95866995</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19_FRST_AK_3</t>
+          <t>1128_AN_TJ_2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C19">
-        <v>-148.72152778</v>
+        <v>-162.29719755</v>
       </c>
       <c r="D19">
-        <v>69.67477778</v>
+        <v>67.95823360999999</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20_FRST_AK_3</t>
+          <t>1129_AN_TJ_2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C20">
-        <v>-148.72172222</v>
+        <v>-162.30217606</v>
       </c>
       <c r="D20">
-        <v>69.67486110999999</v>
+        <v>67.95699938</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>40_FRST_AK_2</t>
+          <t>1130_AN_TJ_2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C21">
-        <v>-148.46638889</v>
+        <v>-162.30751207</v>
       </c>
       <c r="D21">
-        <v>70.16152778</v>
+        <v>67.95753138000001</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>41_FRST_AK_2</t>
+          <t>398_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -748,16 +853,21 @@
         </is>
       </c>
       <c r="C22">
-        <v>-148.46652778</v>
+        <v>-157.38466</v>
       </c>
       <c r="D22">
-        <v>70.16163889000001</v>
+        <v>70.46399099999999</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>42_FRST_AK_2</t>
+          <t>399_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -766,16 +876,21 @@
         </is>
       </c>
       <c r="C23">
-        <v>-148.46908333</v>
+        <v>-157.369637</v>
       </c>
       <c r="D23">
-        <v>70.16069444</v>
+        <v>70.44952000000001</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>43_FRST_AK_2</t>
+          <t>401_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -784,16 +899,21 @@
         </is>
       </c>
       <c r="C24">
-        <v>-148.46658333</v>
+        <v>-157.360005</v>
       </c>
       <c r="D24">
-        <v>70.16152778</v>
+        <v>70.457464</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>44_FRST_AK_2</t>
+          <t>404_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -802,16 +922,21 @@
         </is>
       </c>
       <c r="C25">
-        <v>-148.46905556</v>
+        <v>-157.347504</v>
       </c>
       <c r="D25">
-        <v>70.16072222</v>
+        <v>70.44464000000001</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>45_FRST_AK_2</t>
+          <t>405_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -820,16 +945,21 @@
         </is>
       </c>
       <c r="C26">
-        <v>-148.46666667</v>
+        <v>-157.351898</v>
       </c>
       <c r="D26">
-        <v>70.16180556</v>
+        <v>70.44409400000001</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>48_FRST_AK_2</t>
+          <t>406_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -838,16 +968,21 @@
         </is>
       </c>
       <c r="C27">
-        <v>-148.46666667</v>
+        <v>-157.352724</v>
       </c>
       <c r="D27">
-        <v>70.16155556</v>
+        <v>70.443551</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49_FRST_AK_2</t>
+          <t>407_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -856,16 +991,21 @@
         </is>
       </c>
       <c r="C28">
-        <v>-148.46680556</v>
+        <v>-157.353633</v>
       </c>
       <c r="D28">
-        <v>70.16183332999999</v>
+        <v>70.443685</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>50_FRST_AK_2</t>
+          <t>408_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -874,16 +1014,21 @@
         </is>
       </c>
       <c r="C29">
-        <v>-148.46922222</v>
+        <v>-157.351841</v>
       </c>
       <c r="D29">
-        <v>70.16063889</v>
+        <v>70.446314</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>51_FRST_AK_2</t>
+          <t>409_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -892,358 +1037,458 @@
         </is>
       </c>
       <c r="C30">
-        <v>-148.46891667</v>
+        <v>-157.36635</v>
       </c>
       <c r="D30">
-        <v>70.16061111</v>
+        <v>70.443321</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>334_BRW_PW_1</t>
+          <t>410_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C31">
-        <v>-156.6866993</v>
+        <v>-157.368571</v>
       </c>
       <c r="D31">
-        <v>71.2946814</v>
+        <v>70.44452800000001</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>335_BRW_PW_1</t>
+          <t>411_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C32">
-        <v>-156.6864822</v>
+        <v>-157.368702</v>
       </c>
       <c r="D32">
-        <v>71.2942973</v>
+        <v>70.45171499999999</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>336_BRW_PW_1</t>
+          <t>412_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C33">
-        <v>-156.689706</v>
+        <v>-157.412162</v>
       </c>
       <c r="D33">
-        <v>71.28953129999999</v>
+        <v>70.454553</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>337_BRW_PW_1</t>
+          <t>413_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C34">
-        <v>-156.6808901</v>
+        <v>-157.41238</v>
       </c>
       <c r="D34">
-        <v>71.2888406</v>
+        <v>70.454466</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>338_BRW_PW_1</t>
+          <t>414_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C35">
-        <v>-156.6869346</v>
+        <v>-157.407071</v>
       </c>
       <c r="D35">
-        <v>71.28950879999999</v>
+        <v>70.453548</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>339_BRW_PW_1</t>
+          <t>415_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C36">
-        <v>-156.6794243</v>
+        <v>-157.404277</v>
       </c>
       <c r="D36">
-        <v>71.2888926</v>
+        <v>70.45267</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>340_BRW_PW_1</t>
+          <t>416_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C37">
-        <v>-156.683133</v>
+        <v>-157.399635</v>
       </c>
       <c r="D37">
-        <v>71.2894087</v>
+        <v>70.451464</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>341_BRW_PW_1</t>
+          <t>417_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C38">
-        <v>-156.6901802</v>
+        <v>-157.396149</v>
       </c>
       <c r="D38">
-        <v>71.2895079</v>
+        <v>70.451035</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>342_BRW_PW_1</t>
+          <t>418_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C39">
-        <v>-156.6915138</v>
+        <v>-157.396608</v>
       </c>
       <c r="D39">
-        <v>71.2895759</v>
+        <v>70.450653</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343_BRW_PW_1</t>
+          <t>419_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C40">
-        <v>-156.6826446</v>
+        <v>-157.396696</v>
       </c>
       <c r="D40">
-        <v>71.2882118</v>
+        <v>70.449738</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344_BRW_PW_1</t>
+          <t>420_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C41">
-        <v>-156.6797481</v>
+        <v>-157.395538</v>
       </c>
       <c r="D41">
-        <v>71.28968759999999</v>
+        <v>70.449449</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>345_BRW_PW_1</t>
+          <t>421_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C42">
-        <v>-156.6814983</v>
+        <v>-157.39912</v>
       </c>
       <c r="D42">
-        <v>71.2889426</v>
+        <v>70.451016</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>346_BRW_PW_1</t>
+          <t>422_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C43">
-        <v>-156.6857575</v>
+        <v>-157.403903</v>
       </c>
       <c r="D43">
-        <v>71.2953685</v>
+        <v>70.452179</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>347_BRW_PW_1</t>
+          <t>423_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C44">
-        <v>-156.6891071</v>
+        <v>-157.407337</v>
       </c>
       <c r="D44">
-        <v>71.29456639999999</v>
+        <v>70.45768</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>348_BRW_PW_1</t>
+          <t>424_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C45">
-        <v>-156.6882149</v>
+        <v>-157.40527</v>
       </c>
       <c r="D45">
-        <v>71.2946219</v>
+        <v>70.45871200000001</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>349_BRW_PW_1</t>
+          <t>425_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C46">
-        <v>-156.6626057</v>
+        <v>-157.401696</v>
       </c>
       <c r="D46">
-        <v>71.298154</v>
+        <v>70.46194199999999</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>350_BRW_PW_1</t>
+          <t>426_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C47">
-        <v>-156.6639938</v>
+        <v>-157.406241</v>
       </c>
       <c r="D47">
-        <v>71.29777489999999</v>
+        <v>70.45756799999999</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>351_BRW_PW_1</t>
+          <t>427_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C48">
-        <v>-156.6651671</v>
+        <v>-157.390542</v>
       </c>
       <c r="D48">
-        <v>71.2996662</v>
+        <v>70.463734</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>352_BRW_PW_1</t>
+          <t>428_ATQ_VK_1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C49">
-        <v>-156.6618381</v>
+        <v>-157.391751</v>
       </c>
       <c r="D49">
-        <v>71.2947088</v>
+        <v>70.464316</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>353_BRW_PW_1</t>
+          <t>334_BRW_PW_1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1252,16 +1497,21 @@
         </is>
       </c>
       <c r="C50">
-        <v>-156.6647495</v>
+        <v>-156.6866993</v>
       </c>
       <c r="D50">
-        <v>71.29571660000001</v>
+        <v>71.2946814</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>354_BRW_PW_1</t>
+          <t>335_BRW_PW_1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1270,16 +1520,21 @@
         </is>
       </c>
       <c r="C51">
-        <v>-156.6629414</v>
+        <v>-156.6864822</v>
       </c>
       <c r="D51">
-        <v>71.2965671</v>
+        <v>71.2942973</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>355_BRW_PW_1</t>
+          <t>336_BRW_PW_1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1288,16 +1543,21 @@
         </is>
       </c>
       <c r="C52">
-        <v>-156.6642751</v>
+        <v>-156.689706</v>
       </c>
       <c r="D52">
-        <v>71.2966404</v>
+        <v>71.28953129999999</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>356_BRW_PW_1</t>
+          <t>337_BRW_PW_1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1306,880 +1566,1125 @@
         </is>
       </c>
       <c r="C53">
-        <v>-156.70665</v>
+        <v>-156.6808901</v>
       </c>
       <c r="D53">
-        <v>71.2948167</v>
+        <v>71.2888406</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>398_ATQ_VK_1</t>
+          <t>338_BRW_PW_1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C54">
-        <v>-157.38466</v>
+        <v>-156.6869346</v>
       </c>
       <c r="D54">
-        <v>70.46399099999999</v>
+        <v>71.28950879999999</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>399_ATQ_VK_1</t>
+          <t>339_BRW_PW_1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C55">
-        <v>-157.369637</v>
+        <v>-156.6794243</v>
       </c>
       <c r="D55">
-        <v>70.44952000000001</v>
+        <v>71.2888926</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>401_ATQ_VK_1</t>
+          <t>340_BRW_PW_1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C56">
-        <v>-157.360005</v>
+        <v>-156.683133</v>
       </c>
       <c r="D56">
-        <v>70.457464</v>
+        <v>71.2894087</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>404_ATQ_VK_1</t>
+          <t>341_BRW_PW_1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C57">
-        <v>-157.347504</v>
+        <v>-156.6901802</v>
       </c>
       <c r="D57">
-        <v>70.44464000000001</v>
+        <v>71.2895079</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>405_ATQ_VK_1</t>
+          <t>342_BRW_PW_1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C58">
-        <v>-157.351898</v>
+        <v>-156.6915138</v>
       </c>
       <c r="D58">
-        <v>70.44409400000001</v>
+        <v>71.2895759</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>406_ATQ_VK_1</t>
+          <t>343_BRW_PW_1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C59">
-        <v>-157.352724</v>
+        <v>-156.6826446</v>
       </c>
       <c r="D59">
-        <v>70.443551</v>
+        <v>71.2882118</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>407_ATQ_VK_1</t>
+          <t>344_BRW_PW_1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C60">
-        <v>-157.353633</v>
+        <v>-156.6797481</v>
       </c>
       <c r="D60">
-        <v>70.443685</v>
+        <v>71.28968759999999</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>408_ATQ_VK_1</t>
+          <t>345_BRW_PW_1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C61">
-        <v>-157.351841</v>
+        <v>-156.6814983</v>
       </c>
       <c r="D61">
-        <v>70.446314</v>
+        <v>71.2889426</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>409_ATQ_VK_1</t>
+          <t>346_BRW_PW_1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C62">
-        <v>-157.36635</v>
+        <v>-156.6857575</v>
       </c>
       <c r="D62">
-        <v>70.443321</v>
+        <v>71.2953685</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>410_ATQ_VK_1</t>
+          <t>347_BRW_PW_1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C63">
-        <v>-157.368571</v>
+        <v>-156.6891071</v>
       </c>
       <c r="D63">
-        <v>70.44452800000001</v>
+        <v>71.29456639999999</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>411_ATQ_VK_1</t>
+          <t>348_BRW_PW_1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C64">
-        <v>-157.368702</v>
+        <v>-156.6882149</v>
       </c>
       <c r="D64">
-        <v>70.45171499999999</v>
+        <v>71.2946219</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>412_ATQ_VK_1</t>
+          <t>349_BRW_PW_1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C65">
-        <v>-157.412162</v>
+        <v>-156.6626057</v>
       </c>
       <c r="D65">
-        <v>70.454553</v>
+        <v>71.298154</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>413_ATQ_VK_1</t>
+          <t>350_BRW_PW_1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C66">
-        <v>-157.41238</v>
+        <v>-156.6639938</v>
       </c>
       <c r="D66">
-        <v>70.454466</v>
+        <v>71.29777489999999</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>414_ATQ_VK_1</t>
+          <t>351_BRW_PW_1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C67">
-        <v>-157.407071</v>
+        <v>-156.6651671</v>
       </c>
       <c r="D67">
-        <v>70.453548</v>
+        <v>71.2996662</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>415_ATQ_VK_1</t>
+          <t>352_BRW_PW_1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C68">
-        <v>-157.404277</v>
+        <v>-156.6618381</v>
       </c>
       <c r="D68">
-        <v>70.45267</v>
+        <v>71.2947088</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>416_ATQ_VK_1</t>
+          <t>353_BRW_PW_1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C69">
-        <v>-157.399635</v>
+        <v>-156.6647495</v>
       </c>
       <c r="D69">
-        <v>70.451464</v>
+        <v>71.29571660000001</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>417_ATQ_VK_1</t>
+          <t>354_BRW_PW_1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C70">
-        <v>-157.396149</v>
+        <v>-156.6629414</v>
       </c>
       <c r="D70">
-        <v>70.451035</v>
+        <v>71.2965671</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>418_ATQ_VK_1</t>
+          <t>355_BRW_PW_1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C71">
-        <v>-157.396608</v>
+        <v>-156.6642751</v>
       </c>
       <c r="D71">
-        <v>70.450653</v>
+        <v>71.2966404</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>419_ATQ_VK_1</t>
+          <t>356_BRW_PW_1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C72">
-        <v>-157.396696</v>
+        <v>-156.70665</v>
       </c>
       <c r="D72">
-        <v>70.449738</v>
+        <v>71.2948167</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>420_ATQ_VK_1</t>
+          <t>357_BRW_PW_1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C73">
-        <v>-157.395538</v>
+        <v>-156.7073</v>
       </c>
       <c r="D73">
-        <v>70.449449</v>
+        <v>71.2948667</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>421_ATQ_VK_1</t>
+          <t>358_BRW_PW_1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C74">
-        <v>-157.39912</v>
+        <v>-156.7078667</v>
       </c>
       <c r="D74">
-        <v>70.451016</v>
+        <v>71.2953</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>422_ATQ_VK_1</t>
+          <t>359_BRW_PW_1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C75">
-        <v>-157.403903</v>
+        <v>-156.71065</v>
       </c>
       <c r="D75">
-        <v>70.452179</v>
+        <v>71.29695</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>423_ATQ_VK_1</t>
+          <t>360_BRW_PW_1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C76">
-        <v>-157.407337</v>
+        <v>-156.7009167</v>
       </c>
       <c r="D76">
-        <v>70.45768</v>
+        <v>71.2962167</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>424_ATQ_VK_1</t>
+          <t>361_BRW_PW_1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C77">
-        <v>-157.40527</v>
+        <v>-156.6736344</v>
       </c>
       <c r="D77">
-        <v>70.45871200000001</v>
+        <v>71.2979859</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>425_ATQ_VK_1</t>
+          <t>362_BRW_PW_1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C78">
-        <v>-157.401696</v>
+        <v>-156.6749683</v>
       </c>
       <c r="D78">
-        <v>70.46194199999999</v>
+        <v>71.29844850000001</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>426_ATQ_VK_1</t>
+          <t>363_BRW_PW_1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C79">
-        <v>-157.406241</v>
+        <v>-156.6761167</v>
       </c>
       <c r="D79">
-        <v>70.45756799999999</v>
+        <v>71.29904999999999</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>427_ATQ_VK_1</t>
+          <t>364_BRW_PW_1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C80">
-        <v>-157.390542</v>
+        <v>-156.67365</v>
       </c>
       <c r="D80">
-        <v>70.463734</v>
+        <v>71.29675</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>428_ATQ_VK_1</t>
+          <t>365_BRW_PW_1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C81">
-        <v>-157.391751</v>
+        <v>-156.6763833</v>
       </c>
       <c r="D81">
-        <v>70.464316</v>
+        <v>71.28833330000001</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1040_AN_TJ_1</t>
+          <t>366_BRW_PW_1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C82">
-        <v>-162.73186261</v>
+        <v>-156.6757667</v>
       </c>
       <c r="D82">
-        <v>67.46840754999999</v>
+        <v>71.28883329999999</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1041_AN_TJ_1</t>
+          <t>1365_BRW_VS_1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C83">
-        <v>-162.73045967</v>
+        <v>-156.61157</v>
       </c>
       <c r="D83">
-        <v>67.46940259</v>
+        <v>71.28086</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1042_AN_TJ_1</t>
+          <t>1366_BRW_VS_1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C84">
-        <v>-162.72862475</v>
+        <v>-156.6116</v>
       </c>
       <c r="D84">
-        <v>67.46993353000001</v>
+        <v>71.28089</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1043_AN_TJ_1</t>
+          <t>1367_BRW_VS_1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C85">
-        <v>-162.73046769</v>
+        <v>-156.61145</v>
       </c>
       <c r="D85">
-        <v>67.47082311</v>
+        <v>71.28089</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1044_AN_TJ_1</t>
+          <t>1368_BRW_VS_1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C86">
-        <v>-162.72827019</v>
+        <v>-156.60921</v>
       </c>
       <c r="D86">
-        <v>67.47144795</v>
+        <v>71.2813</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1045_AN_TJ_1</t>
+          <t>1369_BRW_VS_1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C87">
-        <v>-162.72242204</v>
+        <v>-156.60923</v>
       </c>
       <c r="D87">
-        <v>67.4733983</v>
+        <v>71.28134</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1046_AN_TJ_1</t>
+          <t>1370_BRW_VS_1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C88">
-        <v>-162.71976654</v>
+        <v>-156.60933</v>
       </c>
       <c r="D88">
-        <v>67.47238161</v>
+        <v>71.28134</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1047_AN_TJ_1</t>
+          <t>1371_BRW_VS_1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C89">
-        <v>-162.71556098</v>
+        <v>-156.61028</v>
       </c>
       <c r="D89">
-        <v>67.46938401</v>
+        <v>71.28163000000001</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1048_AN_TJ_1</t>
+          <t>1372_BRW_VS_1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C90">
-        <v>-162.71556098</v>
+        <v>-156.61038</v>
       </c>
       <c r="D90">
-        <v>67.46938401</v>
+        <v>71.28165</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1049_AN_TJ_1</t>
+          <t>1373_BRW_VS_1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C91">
-        <v>-162.71252794</v>
+        <v>-156.61044</v>
       </c>
       <c r="D91">
-        <v>67.46938523999999</v>
+        <v>71.28167000000001</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1121_AN_TJ_2</t>
+          <t>1374_BRW_VS_1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C92">
-        <v>-162.3071079</v>
+        <v>-156.61149</v>
       </c>
       <c r="D92">
-        <v>67.96023532</v>
+        <v>71.28157</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1122_AN_TJ_2</t>
+          <t>1375_BRW_VS_1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C93">
-        <v>-162.30820942</v>
+        <v>-156.61157</v>
       </c>
       <c r="D93">
-        <v>67.96015801</v>
+        <v>71.28156</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1123_AN_TJ_2</t>
+          <t>1376_BRW_VS_1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C94">
-        <v>-162.30826366</v>
+        <v>-156.61166</v>
       </c>
       <c r="D94">
-        <v>67.96050605000001</v>
+        <v>71.28157</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1124_AN_TJ_2</t>
+          <t>1377_BRW_VS_1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C95">
-        <v>-162.3115999</v>
+        <v>-156.60505</v>
       </c>
       <c r="D95">
-        <v>67.95979371999999</v>
+        <v>71.27916999999999</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1125_AN_TJ_2</t>
+          <t>1378_BRW_VS_1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C96">
-        <v>-162.31303584</v>
+        <v>-156.60495</v>
       </c>
       <c r="D96">
-        <v>67.95891485999999</v>
+        <v>71.27914</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1126_AN_TJ_2</t>
+          <t>1379_BRW_VS_1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C97">
-        <v>-162.31208496</v>
+        <v>-156.60489</v>
       </c>
       <c r="D97">
-        <v>67.95923406999999</v>
+        <v>71.27914</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1127_AN_TJ_2</t>
+          <t>1380_BRW_VS_1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C98">
-        <v>-162.30292467</v>
+        <v>-156.60375</v>
       </c>
       <c r="D98">
-        <v>67.95866995</v>
+        <v>71.27958</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1128_AN_TJ_2</t>
+          <t>1381_BRW_VS_1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C99">
-        <v>-162.29719755</v>
+        <v>-156.60372</v>
       </c>
       <c r="D99">
-        <v>67.95823360999999</v>
+        <v>71.27955</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1129_AN_TJ_2</t>
+          <t>1382_BRW_VS_1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C100">
-        <v>-162.30217606</v>
+        <v>-156.60367</v>
       </c>
       <c r="D100">
-        <v>67.95699938</v>
+        <v>71.27952999999999</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1130_AN_TJ_2</t>
+          <t>1383_BRW_VS_1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C101">
-        <v>-162.30751207</v>
+        <v>-156.60312</v>
       </c>
       <c r="D101">
-        <v>67.95753138000001</v>
+        <v>71.27970000000001</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1365_BRW_VS_1</t>
+          <t>1384_BRW_VS_1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2188,16 +2693,21 @@
         </is>
       </c>
       <c r="C102">
-        <v>-156.61157</v>
+        <v>-156.60306</v>
       </c>
       <c r="D102">
-        <v>71.28086</v>
+        <v>71.27973</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1366_BRW_VS_1</t>
+          <t>1385_BRW_VS_1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2206,16 +2716,21 @@
         </is>
       </c>
       <c r="C103">
-        <v>-156.6116</v>
+        <v>-156.60304</v>
       </c>
       <c r="D103">
-        <v>71.28089</v>
+        <v>71.27975000000001</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1367_BRW_VS_1</t>
+          <t>1386_BRW_VS_1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2224,16 +2739,21 @@
         </is>
       </c>
       <c r="C104">
-        <v>-156.61145</v>
+        <v>-156.60204</v>
       </c>
       <c r="D104">
-        <v>71.28089</v>
+        <v>71.27942</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1368_BRW_VS_1</t>
+          <t>1387_BRW_VS_1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2242,16 +2762,21 @@
         </is>
       </c>
       <c r="C105">
-        <v>-156.60921</v>
+        <v>-156.60215</v>
       </c>
       <c r="D105">
-        <v>71.2813</v>
+        <v>71.27945</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1369_BRW_VS_1</t>
+          <t>1388_BRW_VS_1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2260,16 +2785,21 @@
         </is>
       </c>
       <c r="C106">
-        <v>-156.60923</v>
+        <v>-156.60217</v>
       </c>
       <c r="D106">
-        <v>71.28134</v>
+        <v>71.27947</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1370_BRW_VS_1</t>
+          <t>1389_BRW_VS_1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2278,16 +2808,21 @@
         </is>
       </c>
       <c r="C107">
-        <v>-156.60933</v>
+        <v>-156.60106</v>
       </c>
       <c r="D107">
-        <v>71.28134</v>
+        <v>71.27972</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1371_BRW_VS_1</t>
+          <t>1390_BRW_VS_1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2296,16 +2831,21 @@
         </is>
       </c>
       <c r="C108">
-        <v>-156.61028</v>
+        <v>-156.6012</v>
       </c>
       <c r="D108">
-        <v>71.28163000000001</v>
+        <v>71.27969</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1372_BRW_VS_1</t>
+          <t>1391_BRW_VS_1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2314,16 +2854,21 @@
         </is>
       </c>
       <c r="C109">
-        <v>-156.61038</v>
+        <v>-156.60113</v>
       </c>
       <c r="D109">
-        <v>71.28165</v>
+        <v>71.27967</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1373_BRW_VS_1</t>
+          <t>1392_BRW_VS_1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2332,16 +2877,21 @@
         </is>
       </c>
       <c r="C110">
-        <v>-156.61044</v>
+        <v>-156.59978</v>
       </c>
       <c r="D110">
-        <v>71.28167000000001</v>
+        <v>71.28058</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1374_BRW_VS_1</t>
+          <t>1393_BRW_VS_1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2350,16 +2900,21 @@
         </is>
       </c>
       <c r="C111">
-        <v>-156.61149</v>
+        <v>-156.59968</v>
       </c>
       <c r="D111">
-        <v>71.28157</v>
+        <v>71.28055999999999</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1375_BRW_VS_1</t>
+          <t>1394_BRW_VS_1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2368,16 +2923,21 @@
         </is>
       </c>
       <c r="C112">
-        <v>-156.61157</v>
+        <v>-156.59961</v>
       </c>
       <c r="D112">
-        <v>71.28156</v>
+        <v>71.28055999999999</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1376_BRW_VS_1</t>
+          <t>1395_BRW_VS_1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2386,16 +2946,21 @@
         </is>
       </c>
       <c r="C113">
-        <v>-156.61166</v>
+        <v>-156.5998</v>
       </c>
       <c r="D113">
-        <v>71.28157</v>
+        <v>71.28035</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1377_BRW_VS_1</t>
+          <t>1396_BRW_VS_1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2404,16 +2969,21 @@
         </is>
       </c>
       <c r="C114">
-        <v>-156.60505</v>
+        <v>-156.59996</v>
       </c>
       <c r="D114">
-        <v>71.27916999999999</v>
+        <v>71.28037</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1378_BRW_VS_1</t>
+          <t>1397_BRW_VS_1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2422,16 +2992,21 @@
         </is>
       </c>
       <c r="C115">
-        <v>-156.60495</v>
+        <v>-156.60004</v>
       </c>
       <c r="D115">
-        <v>71.27914</v>
+        <v>71.28037</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1379_BRW_VS_1</t>
+          <t>1398_BRW_VS_1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2440,16 +3015,21 @@
         </is>
       </c>
       <c r="C116">
-        <v>-156.60489</v>
+        <v>-156.59972</v>
       </c>
       <c r="D116">
-        <v>71.27914</v>
+        <v>71.27988999999999</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1380_BRW_VS_1</t>
+          <t>1399_BRW_VS_1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2458,16 +3038,21 @@
         </is>
       </c>
       <c r="C117">
-        <v>-156.60375</v>
+        <v>-156.59964</v>
       </c>
       <c r="D117">
-        <v>71.27958</v>
+        <v>71.27992</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1381_BRW_VS_1</t>
+          <t>1400_BRW_VS_1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2476,16 +3061,21 @@
         </is>
       </c>
       <c r="C118">
-        <v>-156.60372</v>
+        <v>-156.59957</v>
       </c>
       <c r="D118">
-        <v>71.27955</v>
+        <v>71.27992999999999</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1382_BRW_VS_1</t>
+          <t>1401_BRW_VS_1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2494,16 +3084,21 @@
         </is>
       </c>
       <c r="C119">
-        <v>-156.60367</v>
+        <v>-156.6004</v>
       </c>
       <c r="D119">
-        <v>71.27952999999999</v>
+        <v>71.28179</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1383_BRW_VS_1</t>
+          <t>1402_BRW_VS_1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2512,16 +3107,21 @@
         </is>
       </c>
       <c r="C120">
-        <v>-156.60312</v>
+        <v>-156.60042</v>
       </c>
       <c r="D120">
-        <v>71.27970000000001</v>
+        <v>71.28176000000001</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1384_BRW_VS_1</t>
+          <t>1403_BRW_VS_1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2530,16 +3130,21 @@
         </is>
       </c>
       <c r="C121">
-        <v>-156.60306</v>
+        <v>-156.60041</v>
       </c>
       <c r="D121">
-        <v>71.27973</v>
+        <v>71.28174</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1385_BRW_VS_1</t>
+          <t>1404_BRW_VS_1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2548,16 +3153,21 @@
         </is>
       </c>
       <c r="C122">
-        <v>-156.60304</v>
+        <v>-156.60039</v>
       </c>
       <c r="D122">
-        <v>71.27975000000001</v>
+        <v>71.28198</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1386_BRW_VS_1</t>
+          <t>1405_BRW_VS_1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2566,16 +3176,21 @@
         </is>
       </c>
       <c r="C123">
-        <v>-156.60204</v>
+        <v>-156.60042</v>
       </c>
       <c r="D123">
-        <v>71.27942</v>
+        <v>71.28203999999999</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1387_BRW_VS_1</t>
+          <t>1406_BRW_VS_1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2584,16 +3199,21 @@
         </is>
       </c>
       <c r="C124">
-        <v>-156.60215</v>
+        <v>-156.60041</v>
       </c>
       <c r="D124">
-        <v>71.27945</v>
+        <v>71.28206</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1388_BRW_VS_1</t>
+          <t>1407_BRW_VS_1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2602,16 +3222,21 @@
         </is>
       </c>
       <c r="C125">
-        <v>-156.60217</v>
+        <v>-156.60145</v>
       </c>
       <c r="D125">
-        <v>71.27947</v>
+        <v>71.28216</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1389_BRW_VS_1</t>
+          <t>1408_BRW_VS_1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2620,16 +3245,21 @@
         </is>
       </c>
       <c r="C126">
-        <v>-156.60106</v>
+        <v>-156.60155</v>
       </c>
       <c r="D126">
-        <v>71.27972</v>
+        <v>71.28215</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1390_BRW_VS_1</t>
+          <t>1409_BRW_VS_1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2638,16 +3268,21 @@
         </is>
       </c>
       <c r="C127">
-        <v>-156.6012</v>
+        <v>-156.60162</v>
       </c>
       <c r="D127">
-        <v>71.27969</v>
+        <v>71.28214</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1391_BRW_VS_1</t>
+          <t>1410_BRW_VS_1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2656,16 +3291,21 @@
         </is>
       </c>
       <c r="C128">
-        <v>-156.60113</v>
+        <v>-156.59988</v>
       </c>
       <c r="D128">
-        <v>71.27967</v>
+        <v>71.28143</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1392_BRW_VS_1</t>
+          <t>1411_BRW_VS_1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2674,16 +3314,21 @@
         </is>
       </c>
       <c r="C129">
-        <v>-156.59978</v>
+        <v>-156.6</v>
       </c>
       <c r="D129">
-        <v>71.28058</v>
+        <v>71.28146</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1393_BRW_VS_1</t>
+          <t>1412_BRW_VS_1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2692,16 +3337,21 @@
         </is>
       </c>
       <c r="C130">
-        <v>-156.59968</v>
+        <v>-156.60006</v>
       </c>
       <c r="D130">
-        <v>71.28055999999999</v>
+        <v>71.28145000000001</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1394_BRW_VS_1</t>
+          <t>1512_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2710,16 +3360,21 @@
         </is>
       </c>
       <c r="C131">
-        <v>-156.59961</v>
+        <v>-156.60839</v>
       </c>
       <c r="D131">
-        <v>71.28055999999999</v>
+        <v>71.32102</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1395_BRW_VS_1</t>
+          <t>1513_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2728,16 +3383,21 @@
         </is>
       </c>
       <c r="C132">
-        <v>-156.5998</v>
+        <v>-156.60924</v>
       </c>
       <c r="D132">
-        <v>71.28035</v>
+        <v>71.32102</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1396_BRW_VS_1</t>
+          <t>1514_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2746,16 +3406,21 @@
         </is>
       </c>
       <c r="C133">
-        <v>-156.59996</v>
+        <v>-156.60923</v>
       </c>
       <c r="D133">
-        <v>71.28037</v>
+        <v>71.32118</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1397_BRW_VS_1</t>
+          <t>1515_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2764,16 +3429,21 @@
         </is>
       </c>
       <c r="C134">
-        <v>-156.60004</v>
+        <v>-156.60919</v>
       </c>
       <c r="D134">
-        <v>71.28037</v>
+        <v>71.32136</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1398_BRW_VS_1</t>
+          <t>1516_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2782,16 +3452,21 @@
         </is>
       </c>
       <c r="C135">
-        <v>-156.59972</v>
+        <v>-156.60918</v>
       </c>
       <c r="D135">
-        <v>71.27988999999999</v>
+        <v>71.32153</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1399_BRW_VS_1</t>
+          <t>1517_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2800,16 +3475,21 @@
         </is>
       </c>
       <c r="C136">
-        <v>-156.59964</v>
+        <v>-156.60874</v>
       </c>
       <c r="D136">
-        <v>71.27992</v>
+        <v>71.32487999999999</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1400_BRW_VS_1</t>
+          <t>1518_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2818,16 +3498,21 @@
         </is>
       </c>
       <c r="C137">
-        <v>-156.59957</v>
+        <v>-156.60867</v>
       </c>
       <c r="D137">
-        <v>71.27992999999999</v>
+        <v>71.32504</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1401_BRW_VS_1</t>
+          <t>1519_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2836,16 +3521,21 @@
         </is>
       </c>
       <c r="C138">
-        <v>-156.6004</v>
+        <v>-156.60809</v>
       </c>
       <c r="D138">
-        <v>71.28179</v>
+        <v>71.32487</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1402_BRW_VS_1</t>
+          <t>1520_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2854,16 +3544,21 @@
         </is>
       </c>
       <c r="C139">
-        <v>-156.60042</v>
+        <v>-156.60797</v>
       </c>
       <c r="D139">
-        <v>71.28176000000001</v>
+        <v>71.32436</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1403_BRW_VS_1</t>
+          <t>1521_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2872,16 +3567,21 @@
         </is>
       </c>
       <c r="C140">
-        <v>-156.60041</v>
+        <v>-156.60796</v>
       </c>
       <c r="D140">
-        <v>71.28174</v>
+        <v>71.32413</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1404_BRW_VS_1</t>
+          <t>1522_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2890,16 +3590,21 @@
         </is>
       </c>
       <c r="C141">
-        <v>-156.60039</v>
+        <v>-156.60446</v>
       </c>
       <c r="D141">
-        <v>71.28198</v>
+        <v>71.32132</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1405_BRW_VS_1</t>
+          <t>1523_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2908,16 +3613,21 @@
         </is>
       </c>
       <c r="C142">
-        <v>-156.60042</v>
+        <v>-156.60497</v>
       </c>
       <c r="D142">
-        <v>71.28203999999999</v>
+        <v>71.32143000000001</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1406_BRW_VS_1</t>
+          <t>1524_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2926,16 +3636,21 @@
         </is>
       </c>
       <c r="C143">
-        <v>-156.60041</v>
+        <v>-156.6056</v>
       </c>
       <c r="D143">
-        <v>71.28206</v>
+        <v>71.32152000000001</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1407_BRW_VS_1</t>
+          <t>1525_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2944,16 +3659,21 @@
         </is>
       </c>
       <c r="C144">
-        <v>-156.60145</v>
+        <v>-156.60623</v>
       </c>
       <c r="D144">
-        <v>71.28216</v>
+        <v>71.3218</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1408_BRW_VS_1</t>
+          <t>1526_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2962,16 +3682,21 @@
         </is>
       </c>
       <c r="C145">
-        <v>-156.60155</v>
+        <v>-156.60659</v>
       </c>
       <c r="D145">
-        <v>71.28215</v>
+        <v>71.32205</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1409_BRW_VS_1</t>
+          <t>1527_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2980,16 +3705,21 @@
         </is>
       </c>
       <c r="C146">
-        <v>-156.60162</v>
+        <v>-156.60472</v>
       </c>
       <c r="D146">
-        <v>71.28214</v>
+        <v>71.32136</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1410_BRW_VS_1</t>
+          <t>1528_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2998,16 +3728,21 @@
         </is>
       </c>
       <c r="C147">
-        <v>-156.59988</v>
+        <v>-156.6053</v>
       </c>
       <c r="D147">
-        <v>71.28143</v>
+        <v>71.32144</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1411_BRW_VS_1</t>
+          <t>1529_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3016,16 +3751,21 @@
         </is>
       </c>
       <c r="C148">
-        <v>-156.6</v>
+        <v>-156.60561</v>
       </c>
       <c r="D148">
-        <v>71.28146</v>
+        <v>71.32162</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1412_BRW_VS_1</t>
+          <t>1530_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3034,538 +3774,688 @@
         </is>
       </c>
       <c r="C149">
-        <v>-156.60006</v>
+        <v>-156.60642</v>
       </c>
       <c r="D149">
-        <v>71.28145000000001</v>
+        <v>71.32187</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1413_PRUARC_DW_1</t>
+          <t>1531_FLXTWRZONA_SD_1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C150">
-        <v>-148.47140805</v>
+        <v>-156.60682</v>
       </c>
       <c r="D150">
-        <v>70.22317916</v>
+        <v>71.32208</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1414_PRUARC_DW_1</t>
+          <t>1452_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C151">
-        <v>-148.4716756</v>
+        <v>-156.61326</v>
       </c>
       <c r="D151">
-        <v>70.22321881000001</v>
+        <v>71.28122</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1415_PRUARC_DW_1</t>
+          <t>1453_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C152">
-        <v>-148.4713593</v>
+        <v>-156.61441</v>
       </c>
       <c r="D152">
-        <v>70.22322543999999</v>
+        <v>71.28103</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1416_PRUARC_DW_1</t>
+          <t>1454_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C153">
-        <v>-148.47172629</v>
+        <v>-156.61432</v>
       </c>
       <c r="D153">
-        <v>70.22329396000001</v>
+        <v>71.28126</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1417_PRUARC_DW_1</t>
+          <t>1455_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C154">
-        <v>-148.47109754</v>
+        <v>-156.61422</v>
       </c>
       <c r="D154">
-        <v>70.22333270999999</v>
+        <v>71.28161</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1418_PRUARC_DW_1</t>
+          <t>1456_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C155">
-        <v>-148.47151315</v>
+        <v>-156.61467</v>
       </c>
       <c r="D155">
-        <v>70.22337813</v>
+        <v>71.28131</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1419_PRUARC_DW_1</t>
+          <t>1457_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C156">
-        <v>-148.47095379</v>
+        <v>-156.61424</v>
       </c>
       <c r="D156">
-        <v>70.22356864</v>
+        <v>71.28081</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1420_PRUARC_DW_1</t>
+          <t>1458_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C157">
-        <v>-148.47124487</v>
+        <v>-156.61436</v>
       </c>
       <c r="D157">
-        <v>70.22360955000001</v>
+        <v>71.28049</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1421_PRUARC_DW_1</t>
+          <t>1459_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C158">
-        <v>-148.47024093</v>
+        <v>-156.61271</v>
       </c>
       <c r="D158">
-        <v>70.22394567000001</v>
+        <v>71.28062</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1422_PRUARC_DW_1</t>
+          <t>1460_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C159">
-        <v>-148.47028424</v>
+        <v>-156.61238</v>
       </c>
       <c r="D159">
-        <v>70.22399661</v>
+        <v>71.2804</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1423_PRUARC_DW_1</t>
+          <t>1461_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C160">
-        <v>-148.4691739</v>
+        <v>-156.61278</v>
       </c>
       <c r="D160">
-        <v>70.22478794</v>
+        <v>71.28004</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1424_PRUARC_DW_1</t>
+          <t>1462_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C161">
-        <v>-148.46932532</v>
+        <v>-156.61001</v>
       </c>
       <c r="D161">
-        <v>70.22478943</v>
+        <v>71.2795</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1425_PRUARC_DW_1</t>
+          <t>1463_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C162">
-        <v>-148.47125808</v>
+        <v>-156.6097</v>
       </c>
       <c r="D162">
-        <v>70.22291749999999</v>
+        <v>71.27937</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1426_PRUARC_DW_1</t>
+          <t>1464_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C163">
-        <v>-148.47091</v>
+        <v>-156.61027</v>
       </c>
       <c r="D163">
-        <v>70.22287111999999</v>
+        <v>71.2792</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1427_PRUARC_DW_1</t>
+          <t>1465_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C164">
-        <v>-148.47125468</v>
+        <v>-156.6103</v>
       </c>
       <c r="D164">
-        <v>70.22287787</v>
+        <v>71.27903000000001</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1428_PRUARC_DW_1</t>
+          <t>1466_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C165">
-        <v>-148.47143883</v>
+        <v>-156.61058</v>
       </c>
       <c r="D165">
-        <v>70.22289397999999</v>
+        <v>71.27867000000001</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1429_PRUARC_DW_1</t>
+          <t>1467_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C166">
-        <v>-148.47148563</v>
+        <v>-156.61043</v>
       </c>
       <c r="D166">
-        <v>70.22277081</v>
+        <v>71.27885999999999</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1430_PRUARC_DW_1</t>
+          <t>1468_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C167">
-        <v>-148.47163501</v>
+        <v>-156.61004</v>
       </c>
       <c r="D167">
-        <v>70.22277261000001</v>
+        <v>71.27849999999999</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1431_PRUARC_DW_1</t>
+          <t>1469_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C168">
-        <v>-148.47176882</v>
+        <v>-156.61017</v>
       </c>
       <c r="D168">
-        <v>70.22259928</v>
+        <v>71.27833</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1432_PRUARC_DW_1</t>
+          <t>1470_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C169">
-        <v>-148.47197271</v>
+        <v>-156.6098</v>
       </c>
       <c r="D169">
-        <v>70.22258632</v>
+        <v>71.27833</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1433_PRUARC_DW_1</t>
+          <t>1471_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C170">
-        <v>-148.47251118</v>
+        <v>-156.60975</v>
       </c>
       <c r="D170">
-        <v>70.22215088999999</v>
+        <v>71.27819</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1434_PRUARC_DW_1</t>
+          <t>1472_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C171">
-        <v>-148.4724173</v>
+        <v>-156.61373</v>
       </c>
       <c r="D171">
-        <v>70.2220621</v>
+        <v>71.28082000000001</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1435_PRUARC_DW_1</t>
+          <t>1473_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C172">
-        <v>-148.47353697</v>
+        <v>-156.61333</v>
       </c>
       <c r="D172">
-        <v>70.22136116999999</v>
+        <v>71.28032</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1436_PRUARC_DW_1</t>
+          <t>1474_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C173">
-        <v>-148.47367271</v>
+        <v>-156.6122</v>
       </c>
       <c r="D173">
-        <v>70.22136857</v>
+        <v>71.28026</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1437_PRUARC_DW_1</t>
+          <t>1475_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C174">
-        <v>-148.4714481</v>
+        <v>-156.61167</v>
       </c>
       <c r="D174">
-        <v>70.22315542</v>
+        <v>71.28084</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1438_PRUARC_DW_1</t>
+          <t>1476_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C175">
-        <v>-148.46774151</v>
+        <v>-156.61142</v>
       </c>
       <c r="D175">
-        <v>70.2224595</v>
+        <v>71.28109000000001</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1439_PRUARC_DW_1</t>
+          <t>1477_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C176">
-        <v>-148.46782079</v>
+        <v>-156.6104</v>
       </c>
       <c r="D176">
-        <v>70.22243082999999</v>
+        <v>71.28079</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1440_PRUARC_DW_1</t>
+          <t>1478_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C177">
-        <v>-148.46585804</v>
+        <v>-156.61014</v>
       </c>
       <c r="D177">
-        <v>70.22689676</v>
+        <v>71.28068</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1441_PRUARC_DW_1</t>
+          <t>1479_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C178">
-        <v>-148.46728725</v>
+        <v>-156.61025</v>
       </c>
       <c r="D178">
-        <v>70.22610928</v>
+        <v>71.28103</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>357_BRW_PW_1</t>
+          <t>1480_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3574,16 +4464,21 @@
         </is>
       </c>
       <c r="C179">
-        <v>-156.7073</v>
+        <v>-156.61151</v>
       </c>
       <c r="D179">
-        <v>71.2948667</v>
+        <v>71.28171</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>358_BRW_PW_1</t>
+          <t>1481_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3592,16 +4487,21 @@
         </is>
       </c>
       <c r="C180">
-        <v>-156.7078667</v>
+        <v>-156.61174</v>
       </c>
       <c r="D180">
-        <v>71.2953</v>
+        <v>71.28207</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>359_BRW_PW_1</t>
+          <t>1482_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3610,16 +4510,21 @@
         </is>
       </c>
       <c r="C181">
-        <v>-156.71065</v>
+        <v>-156.61393</v>
       </c>
       <c r="D181">
-        <v>71.29695</v>
+        <v>71.2812</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>360_BRW_PW_1</t>
+          <t>1483_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3628,16 +4533,21 @@
         </is>
       </c>
       <c r="C182">
-        <v>-156.7009167</v>
+        <v>-156.61381</v>
       </c>
       <c r="D182">
-        <v>71.2962167</v>
+        <v>71.28086</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>361_BRW_PW_1</t>
+          <t>1484_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3646,16 +4556,21 @@
         </is>
       </c>
       <c r="C183">
-        <v>-156.6736344</v>
+        <v>-156.6144</v>
       </c>
       <c r="D183">
-        <v>71.2979859</v>
+        <v>71.28045</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>362_BRW_PW_1</t>
+          <t>1485_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3664,16 +4579,21 @@
         </is>
       </c>
       <c r="C184">
-        <v>-156.6749683</v>
+        <v>-156.61264</v>
       </c>
       <c r="D184">
-        <v>71.29844850000001</v>
+        <v>71.28053</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>363_BRW_PW_1</t>
+          <t>1486_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3682,16 +4602,21 @@
         </is>
       </c>
       <c r="C185">
-        <v>-156.6761167</v>
+        <v>-156.61255</v>
       </c>
       <c r="D185">
-        <v>71.29904999999999</v>
+        <v>71.2803</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>364_BRW_PW_1</t>
+          <t>1487_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3700,16 +4625,21 @@
         </is>
       </c>
       <c r="C186">
-        <v>-156.67365</v>
+        <v>-156.6121</v>
       </c>
       <c r="D186">
-        <v>71.29675</v>
+        <v>71.28017</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>365_BRW_PW_1</t>
+          <t>1488_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3718,16 +4648,21 @@
         </is>
       </c>
       <c r="C187">
-        <v>-156.6763833</v>
+        <v>-156.61176</v>
       </c>
       <c r="D187">
-        <v>71.28833330000001</v>
+        <v>71.28085</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>366_BRW_PW_1</t>
+          <t>1489_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3736,16 +4671,21 @@
         </is>
       </c>
       <c r="C188">
-        <v>-156.6757667</v>
+        <v>-156.61188</v>
       </c>
       <c r="D188">
-        <v>71.28883329999999</v>
+        <v>71.28118000000001</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1452_FLXTWRZONA_SD_2</t>
+          <t>1490_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3754,16 +4694,21 @@
         </is>
       </c>
       <c r="C189">
-        <v>-156.61326</v>
+        <v>-156.61089</v>
       </c>
       <c r="D189">
-        <v>71.28122</v>
+        <v>71.28106</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1453_FLXTWRZONA_SD_2</t>
+          <t>1491_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3772,16 +4717,21 @@
         </is>
       </c>
       <c r="C190">
-        <v>-156.61441</v>
+        <v>-156.6106</v>
       </c>
       <c r="D190">
-        <v>71.28103</v>
+        <v>71.28126</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1454_FLXTWRZONA_SD_2</t>
+          <t>1492_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3790,16 +4740,21 @@
         </is>
       </c>
       <c r="C191">
-        <v>-156.61432</v>
+        <v>-156.61358</v>
       </c>
       <c r="D191">
-        <v>71.28126</v>
+        <v>71.28121</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1455_FLXTWRZONA_SD_2</t>
+          <t>1493_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3808,16 +4763,21 @@
         </is>
       </c>
       <c r="C192">
-        <v>-156.61422</v>
+        <v>-156.61457</v>
       </c>
       <c r="D192">
-        <v>71.28161</v>
+        <v>71.28139</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1456_FLXTWRZONA_SD_2</t>
+          <t>1494_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3826,16 +4786,21 @@
         </is>
       </c>
       <c r="C193">
-        <v>-156.61467</v>
+        <v>-156.61482</v>
       </c>
       <c r="D193">
-        <v>71.28131</v>
+        <v>71.28077999999999</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1457_FLXTWRZONA_SD_2</t>
+          <t>1495_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3844,16 +4809,21 @@
         </is>
       </c>
       <c r="C194">
-        <v>-156.61424</v>
+        <v>-156.61351</v>
       </c>
       <c r="D194">
-        <v>71.28081</v>
+        <v>71.28028</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1458_FLXTWRZONA_SD_2</t>
+          <t>1496_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3862,16 +4832,21 @@
         </is>
       </c>
       <c r="C195">
-        <v>-156.61436</v>
+        <v>-156.61309</v>
       </c>
       <c r="D195">
-        <v>71.28049</v>
+        <v>71.28044</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1459_FLXTWRZONA_SD_2</t>
+          <t>1497_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3880,16 +4855,21 @@
         </is>
       </c>
       <c r="C196">
-        <v>-156.61271</v>
+        <v>-156.61209</v>
       </c>
       <c r="D196">
-        <v>71.28062</v>
+        <v>71.28019</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1460_FLXTWRZONA_SD_2</t>
+          <t>1498_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3898,16 +4878,21 @@
         </is>
       </c>
       <c r="C197">
-        <v>-156.61238</v>
+        <v>-156.61189</v>
       </c>
       <c r="D197">
-        <v>71.2804</v>
+        <v>71.28085</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1461_FLXTWRZONA_SD_2</t>
+          <t>1499_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3916,16 +4901,21 @@
         </is>
       </c>
       <c r="C198">
-        <v>-156.61278</v>
+        <v>-156.61047</v>
       </c>
       <c r="D198">
-        <v>71.28004</v>
+        <v>71.28122</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1462_FLXTWRZONA_SD_2</t>
+          <t>1500_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3934,16 +4924,21 @@
         </is>
       </c>
       <c r="C199">
-        <v>-156.61001</v>
+        <v>-156.61134</v>
       </c>
       <c r="D199">
-        <v>71.2795</v>
+        <v>71.28183</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1463_FLXTWRZONA_SD_2</t>
+          <t>1501_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3952,16 +4947,21 @@
         </is>
       </c>
       <c r="C200">
-        <v>-156.6097</v>
+        <v>-156.61156</v>
       </c>
       <c r="D200">
-        <v>71.27937</v>
+        <v>71.28191</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1464_FLXTWRZONA_SD_2</t>
+          <t>1502_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3970,16 +4970,21 @@
         </is>
       </c>
       <c r="C201">
-        <v>-156.61027</v>
+        <v>-156.59202</v>
       </c>
       <c r="D201">
-        <v>71.2792</v>
+        <v>71.28051000000001</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1465_FLXTWRZONA_SD_2</t>
+          <t>1503_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3988,16 +4993,21 @@
         </is>
       </c>
       <c r="C202">
-        <v>-156.6103</v>
+        <v>-156.59189</v>
       </c>
       <c r="D202">
-        <v>71.27903000000001</v>
+        <v>71.28055000000001</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1466_FLXTWRZONA_SD_2</t>
+          <t>1504_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4006,16 +5016,21 @@
         </is>
       </c>
       <c r="C203">
-        <v>-156.61058</v>
+        <v>-156.59138</v>
       </c>
       <c r="D203">
-        <v>71.27867000000001</v>
+        <v>71.28052</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1467_FLXTWRZONA_SD_2</t>
+          <t>1505_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4024,16 +5039,21 @@
         </is>
       </c>
       <c r="C204">
-        <v>-156.61043</v>
+        <v>-156.59271</v>
       </c>
       <c r="D204">
-        <v>71.27885999999999</v>
+        <v>71.28054</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1468_FLXTWRZONA_SD_2</t>
+          <t>1506_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4042,16 +5062,21 @@
         </is>
       </c>
       <c r="C205">
-        <v>-156.61004</v>
+        <v>-156.59359</v>
       </c>
       <c r="D205">
-        <v>71.27849999999999</v>
+        <v>71.28055999999999</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1469_FLXTWRZONA_SD_2</t>
+          <t>1507_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4060,16 +5085,21 @@
         </is>
       </c>
       <c r="C206">
-        <v>-156.61017</v>
+        <v>-156.59085</v>
       </c>
       <c r="D206">
-        <v>71.27833</v>
+        <v>71.2805</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1470_FLXTWRZONA_SD_2</t>
+          <t>1508_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4078,16 +5108,21 @@
         </is>
       </c>
       <c r="C207">
-        <v>-156.6098</v>
+        <v>-156.59499</v>
       </c>
       <c r="D207">
-        <v>71.27833</v>
+        <v>71.28059</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1471_FLXTWRZONA_SD_2</t>
+          <t>1509_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4096,16 +5131,21 @@
         </is>
       </c>
       <c r="C208">
-        <v>-156.60975</v>
+        <v>-156.59558</v>
       </c>
       <c r="D208">
-        <v>71.27819</v>
+        <v>71.28055999999999</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1472_FLXTWRZONA_SD_2</t>
+          <t>1510_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4114,16 +5154,21 @@
         </is>
       </c>
       <c r="C209">
-        <v>-156.61373</v>
+        <v>-156.59614</v>
       </c>
       <c r="D209">
-        <v>71.28082000000001</v>
+        <v>71.28057</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1473_FLXTWRZONA_SD_2</t>
+          <t>1511_FLXTWRZONA_SD_2</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4132,538 +5177,688 @@
         </is>
       </c>
       <c r="C210">
-        <v>-156.61333</v>
+        <v>-156.59643</v>
       </c>
       <c r="D210">
-        <v>71.28032</v>
+        <v>71.28061</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1474_FLXTWRZONA_SD_2</t>
+          <t>1532_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C211">
-        <v>-156.6122</v>
+        <v>-157.40842</v>
       </c>
       <c r="D211">
-        <v>71.28026</v>
+        <v>70.46968</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1475_FLXTWRZONA_SD_2</t>
+          <t>1533_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C212">
-        <v>-156.61167</v>
+        <v>-157.40611</v>
       </c>
       <c r="D212">
-        <v>71.28084</v>
+        <v>70.47013</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1476_FLXTWRZONA_SD_2</t>
+          <t>1534_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C213">
-        <v>-156.61142</v>
+        <v>-157.40714</v>
       </c>
       <c r="D213">
-        <v>71.28109000000001</v>
+        <v>70.46925</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1477_FLXTWRZONA_SD_2</t>
+          <t>1535_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C214">
-        <v>-156.6104</v>
+        <v>-157.40987</v>
       </c>
       <c r="D214">
-        <v>71.28079</v>
+        <v>70.46847</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1478_FLXTWRZONA_SD_2</t>
+          <t>1536_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C215">
-        <v>-156.61014</v>
+        <v>-157.41043</v>
       </c>
       <c r="D215">
-        <v>71.28068</v>
+        <v>70.4696</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1479_FLXTWRZONA_SD_2</t>
+          <t>1537_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C216">
-        <v>-156.61025</v>
+        <v>-157.41294</v>
       </c>
       <c r="D216">
-        <v>71.28103</v>
+        <v>70.46947</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1480_FLXTWRZONA_SD_2</t>
+          <t>1538_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C217">
-        <v>-156.61151</v>
+        <v>-157.40983</v>
       </c>
       <c r="D217">
-        <v>71.28171</v>
+        <v>70.47036</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1481_FLXTWRZONA_SD_2</t>
+          <t>1539_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C218">
-        <v>-156.61174</v>
+        <v>-157.41069</v>
       </c>
       <c r="D218">
-        <v>71.28207</v>
+        <v>70.47150000000001</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1482_FLXTWRZONA_SD_2</t>
+          <t>1540_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C219">
-        <v>-156.61393</v>
+        <v>-157.40904</v>
       </c>
       <c r="D219">
-        <v>71.2812</v>
+        <v>70.46992</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1483_FLXTWRZONA_SD_2</t>
+          <t>1541_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C220">
-        <v>-156.61381</v>
+        <v>-157.40867</v>
       </c>
       <c r="D220">
-        <v>71.28086</v>
+        <v>70.47075</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1484_FLXTWRZONA_SD_2</t>
+          <t>1542_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C221">
-        <v>-156.6144</v>
+        <v>-157.40674</v>
       </c>
       <c r="D221">
-        <v>71.28045</v>
+        <v>70.47</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1485_FLXTWRZONA_SD_2</t>
+          <t>1543_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C222">
-        <v>-156.61264</v>
+        <v>-157.40674</v>
       </c>
       <c r="D222">
-        <v>71.28053</v>
+        <v>70.46925</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1486_FLXTWRZONA_SD_2</t>
+          <t>1544_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C223">
-        <v>-156.61255</v>
+        <v>-157.40922</v>
       </c>
       <c r="D223">
-        <v>71.2803</v>
+        <v>70.46935999999999</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1487_FLXTWRZONA_SD_2</t>
+          <t>1545_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C224">
-        <v>-156.6121</v>
+        <v>-157.41035</v>
       </c>
       <c r="D224">
-        <v>71.28017</v>
+        <v>70.46804</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1488_FLXTWRZONA_SD_2</t>
+          <t>1546_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C225">
-        <v>-156.61176</v>
+        <v>-157.41096</v>
       </c>
       <c r="D225">
-        <v>71.28085</v>
+        <v>70.46957999999999</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1489_FLXTWRZONA_SD_2</t>
+          <t>1547_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C226">
-        <v>-156.61188</v>
+        <v>-157.41435</v>
       </c>
       <c r="D226">
-        <v>71.28118000000001</v>
+        <v>70.46939999999999</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1490_FLXTWRZONA_SD_2</t>
+          <t>1548_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C227">
-        <v>-156.61089</v>
+        <v>-157.4092</v>
       </c>
       <c r="D227">
-        <v>71.28106</v>
+        <v>70.46974</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1491_FLXTWRZONA_SD_2</t>
+          <t>1549_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C228">
-        <v>-156.6106</v>
+        <v>-157.40997</v>
       </c>
       <c r="D228">
-        <v>71.28126</v>
+        <v>70.47049</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1492_FLXTWRZONA_SD_2</t>
+          <t>1550_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C229">
-        <v>-156.61358</v>
+        <v>-157.40912</v>
       </c>
       <c r="D229">
-        <v>71.28121</v>
+        <v>70.46981</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1493_FLXTWRZONA_SD_2</t>
+          <t>1551_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C230">
-        <v>-156.61457</v>
+        <v>-157.40842</v>
       </c>
       <c r="D230">
-        <v>71.28139</v>
+        <v>70.47087000000001</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1494_FLXTWRZONA_SD_2</t>
+          <t>1552_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C231">
-        <v>-156.61482</v>
+        <v>-157.4056</v>
       </c>
       <c r="D231">
-        <v>71.28077999999999</v>
+        <v>70.47022</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1495_FLXTWRZONA_SD_2</t>
+          <t>1553_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C232">
-        <v>-156.61351</v>
+        <v>-157.40839</v>
       </c>
       <c r="D232">
-        <v>71.28028</v>
+        <v>70.46944999999999</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1496_FLXTWRZONA_SD_2</t>
+          <t>1554_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C233">
-        <v>-156.61309</v>
+        <v>-157.40946</v>
       </c>
       <c r="D233">
-        <v>71.28044</v>
+        <v>70.46872</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1497_FLXTWRZONA_SD_2</t>
+          <t>1555_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C234">
-        <v>-156.61209</v>
+        <v>-157.41046</v>
       </c>
       <c r="D234">
-        <v>71.28019</v>
+        <v>70.46796000000001</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1498_FLXTWRZONA_SD_2</t>
+          <t>1556_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C235">
-        <v>-156.61189</v>
+        <v>-157.41001</v>
       </c>
       <c r="D235">
-        <v>71.28085</v>
+        <v>70.4696</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1499_FLXTWRZONA_SD_2</t>
+          <t>1557_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C236">
-        <v>-156.61047</v>
+        <v>-157.41318</v>
       </c>
       <c r="D236">
-        <v>71.28122</v>
+        <v>70.46944999999999</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1500_FLXTWRZONA_SD_2</t>
+          <t>1558_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C237">
-        <v>-156.61134</v>
+        <v>-157.40967</v>
       </c>
       <c r="D237">
-        <v>71.28183</v>
+        <v>70.4701</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1501_FLXTWRZONA_SD_2</t>
+          <t>1559_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C238">
-        <v>-156.61156</v>
+        <v>-157.41052</v>
       </c>
       <c r="D238">
-        <v>71.28191</v>
+        <v>70.47136999999999</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1502_FLXTWRZONA_SD_2</t>
+          <t>1560_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C239">
-        <v>-156.59202</v>
+        <v>-157.40892</v>
       </c>
       <c r="D239">
-        <v>71.28051000000001</v>
+        <v>70.47064</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1503_FLXTWRZONA_SD_2</t>
+          <t>1561_FLXTWRZONA_SD_3</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4672,556 +5867,711 @@
         </is>
       </c>
       <c r="C240">
-        <v>-156.59189</v>
+        <v>-157.40873</v>
       </c>
       <c r="D240">
-        <v>71.28055000000001</v>
+        <v>70.47162</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1504_FLXTWRZONA_SD_2</t>
+          <t>1562_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C241">
-        <v>-156.59138</v>
+        <v>-155.7532</v>
       </c>
       <c r="D241">
-        <v>71.28052</v>
+        <v>68.48812</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1505_FLXTWRZONA_SD_2</t>
+          <t>1563_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C242">
-        <v>-156.59271</v>
+        <v>-155.75265</v>
       </c>
       <c r="D242">
-        <v>71.28054</v>
+        <v>68.48835</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1506_FLXTWRZONA_SD_2</t>
+          <t>1564_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C243">
-        <v>-156.59359</v>
+        <v>-155.75198</v>
       </c>
       <c r="D243">
-        <v>71.28055999999999</v>
+        <v>68.48863</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1507_FLXTWRZONA_SD_2</t>
+          <t>1565_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C244">
-        <v>-156.59085</v>
+        <v>-155.75139</v>
       </c>
       <c r="D244">
-        <v>71.2805</v>
+        <v>68.48887000000001</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1508_FLXTWRZONA_SD_2</t>
+          <t>1566_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C245">
-        <v>-156.59499</v>
+        <v>-155.75079</v>
       </c>
       <c r="D245">
-        <v>71.28059</v>
+        <v>68.48911</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1509_FLXTWRZONA_SD_2</t>
+          <t>1567_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C246">
-        <v>-156.59558</v>
+        <v>-155.75208</v>
       </c>
       <c r="D246">
-        <v>71.28055999999999</v>
+        <v>68.48912</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1510_FLXTWRZONA_SD_2</t>
+          <t>1568_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C247">
-        <v>-156.59614</v>
+        <v>-155.75279</v>
       </c>
       <c r="D247">
-        <v>71.28057</v>
+        <v>68.48885</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1511_FLXTWRZONA_SD_2</t>
+          <t>1569_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C248">
-        <v>-156.59643</v>
+        <v>-155.75322</v>
       </c>
       <c r="D248">
-        <v>71.28061</v>
+        <v>68.48865000000001</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1512_FLXTWRZONA_SD_1</t>
+          <t>1570_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C249">
-        <v>-156.60839</v>
+        <v>-155.75381</v>
       </c>
       <c r="D249">
-        <v>71.32102</v>
+        <v>68.48845</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1513_FLXTWRZONA_SD_1</t>
+          <t>1571_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C250">
-        <v>-156.60924</v>
+        <v>-155.75447</v>
       </c>
       <c r="D250">
-        <v>71.32102</v>
+        <v>68.48829000000001</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1514_FLXTWRZONA_SD_1</t>
+          <t>1572_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C251">
-        <v>-156.60923</v>
+        <v>-155.75002</v>
       </c>
       <c r="D251">
-        <v>71.32118</v>
+        <v>68.4867</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1515_FLXTWRZONA_SD_1</t>
+          <t>1573_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C252">
-        <v>-156.60919</v>
+        <v>-155.7487</v>
       </c>
       <c r="D252">
-        <v>71.32136</v>
+        <v>68.48675</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1516_FLXTWRZONA_SD_1</t>
+          <t>1574_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C253">
-        <v>-156.60918</v>
+        <v>-155.74717</v>
       </c>
       <c r="D253">
-        <v>71.32153</v>
+        <v>68.4859</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1517_FLXTWRZONA_SD_1</t>
+          <t>1575_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C254">
-        <v>-156.60874</v>
+        <v>-155.74916</v>
       </c>
       <c r="D254">
-        <v>71.32487999999999</v>
+        <v>68.48589</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1518_FLXTWRZONA_SD_1</t>
+          <t>1576_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C255">
-        <v>-156.60867</v>
+        <v>-155.75182</v>
       </c>
       <c r="D255">
-        <v>71.32504</v>
+        <v>68.48565000000001</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1519_FLXTWRZONA_SD_1</t>
+          <t>1577_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C256">
-        <v>-156.60809</v>
+        <v>-155.74873</v>
       </c>
       <c r="D256">
-        <v>71.32487</v>
+        <v>68.4883</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1520_FLXTWRZONA_SD_1</t>
+          <t>1578_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C257">
-        <v>-156.60797</v>
+        <v>-155.74864</v>
       </c>
       <c r="D257">
-        <v>71.32436</v>
+        <v>68.48839</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1521_FLXTWRZONA_SD_1</t>
+          <t>1579_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C258">
-        <v>-156.60796</v>
+        <v>-155.74856</v>
       </c>
       <c r="D258">
-        <v>71.32413</v>
+        <v>68.48851999999999</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1522_FLXTWRZONA_SD_1</t>
+          <t>1580_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C259">
-        <v>-156.60446</v>
+        <v>-155.74834</v>
       </c>
       <c r="D259">
-        <v>71.32132</v>
+        <v>68.48878000000001</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1523_FLXTWRZONA_SD_1</t>
+          <t>1581_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C260">
-        <v>-156.60497</v>
+        <v>-155.74825</v>
       </c>
       <c r="D260">
-        <v>71.32143000000001</v>
+        <v>68.48887000000001</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1524_FLXTWRZONA_SD_1</t>
+          <t>1582_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C261">
-        <v>-156.6056</v>
+        <v>-155.7486</v>
       </c>
       <c r="D261">
-        <v>71.32152000000001</v>
+        <v>68.48896999999999</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1525_FLXTWRZONA_SD_1</t>
+          <t>1583_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C262">
-        <v>-156.60623</v>
+        <v>-155.74891</v>
       </c>
       <c r="D262">
-        <v>71.3218</v>
+        <v>68.4889</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1526_FLXTWRZONA_SD_1</t>
+          <t>1584_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C263">
-        <v>-156.60659</v>
+        <v>-155.74924</v>
       </c>
       <c r="D263">
-        <v>71.32205</v>
+        <v>68.48873</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1527_FLXTWRZONA_SD_1</t>
+          <t>1585_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C264">
-        <v>-156.60472</v>
+        <v>-155.74896</v>
       </c>
       <c r="D264">
-        <v>71.32136</v>
+        <v>68.48855</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1528_FLXTWRZONA_SD_1</t>
+          <t>1586_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C265">
-        <v>-156.6053</v>
+        <v>-155.74897</v>
       </c>
       <c r="D265">
-        <v>71.32144</v>
+        <v>68.4885</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1529_FLXTWRZONA_SD_1</t>
+          <t>1587_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C266">
-        <v>-156.60561</v>
+        <v>-155.7492</v>
       </c>
       <c r="D266">
-        <v>71.32162</v>
+        <v>68.48753000000001</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1530_FLXTWRZONA_SD_1</t>
+          <t>1588_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C267">
-        <v>-156.60642</v>
+        <v>-155.74678</v>
       </c>
       <c r="D267">
-        <v>71.32187</v>
+        <v>68.48724</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1531_FLXTWRZONA_SD_1</t>
+          <t>1589_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C268">
-        <v>-156.60682</v>
+        <v>-155.74938</v>
       </c>
       <c r="D268">
-        <v>71.32208</v>
+        <v>68.48638</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1532_FLXTWRZONA_SD_3</t>
+          <t>1590_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C269">
-        <v>-157.40842</v>
+        <v>-155.74812</v>
       </c>
       <c r="D269">
-        <v>70.46968</v>
+        <v>68.48508</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1533_FLXTWRZONA_SD_3</t>
+          <t>1591_FLXTWRZONA_SD_4</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C270">
-        <v>-157.40611</v>
+        <v>-155.75168</v>
       </c>
       <c r="D270">
-        <v>70.47013</v>
+        <v>68.48714</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1534_FLXTWRZONA_SD_3</t>
+          <t>40_FRST_AK_2</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -5230,16 +6580,21 @@
         </is>
       </c>
       <c r="C271">
-        <v>-157.40714</v>
+        <v>-148.46638889</v>
       </c>
       <c r="D271">
-        <v>70.46925</v>
+        <v>70.16152778</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1535_FLXTWRZONA_SD_3</t>
+          <t>41_FRST_AK_2</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -5248,16 +6603,21 @@
         </is>
       </c>
       <c r="C272">
-        <v>-157.40987</v>
+        <v>-148.46652778</v>
       </c>
       <c r="D272">
-        <v>70.46847</v>
+        <v>70.16163889000001</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1536_FLXTWRZONA_SD_3</t>
+          <t>42_FRST_AK_2</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5266,16 +6626,21 @@
         </is>
       </c>
       <c r="C273">
-        <v>-157.41043</v>
+        <v>-148.46908333</v>
       </c>
       <c r="D273">
-        <v>70.4696</v>
+        <v>70.16069444</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1537_FLXTWRZONA_SD_3</t>
+          <t>43_FRST_AK_2</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5284,16 +6649,21 @@
         </is>
       </c>
       <c r="C274">
-        <v>-157.41294</v>
+        <v>-148.46658333</v>
       </c>
       <c r="D274">
-        <v>70.46947</v>
+        <v>70.16152778</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1538_FLXTWRZONA_SD_3</t>
+          <t>44_FRST_AK_2</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5302,16 +6672,21 @@
         </is>
       </c>
       <c r="C275">
-        <v>-157.40983</v>
+        <v>-148.46905556</v>
       </c>
       <c r="D275">
-        <v>70.47036</v>
+        <v>70.16072222</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1539_FLXTWRZONA_SD_3</t>
+          <t>45_FRST_AK_2</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5320,16 +6695,21 @@
         </is>
       </c>
       <c r="C276">
-        <v>-157.41069</v>
+        <v>-148.46666667</v>
       </c>
       <c r="D276">
-        <v>70.47150000000001</v>
+        <v>70.16180556</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1540_FLXTWRZONA_SD_3</t>
+          <t>48_FRST_AK_2</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5338,16 +6718,21 @@
         </is>
       </c>
       <c r="C277">
-        <v>-157.40904</v>
+        <v>-148.46666667</v>
       </c>
       <c r="D277">
-        <v>70.46992</v>
+        <v>70.16155556</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1541_FLXTWRZONA_SD_3</t>
+          <t>49_FRST_AK_2</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -5356,16 +6741,21 @@
         </is>
       </c>
       <c r="C278">
-        <v>-157.40867</v>
+        <v>-148.46680556</v>
       </c>
       <c r="D278">
-        <v>70.47075</v>
+        <v>70.16183332999999</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1542_FLXTWRZONA_SD_3</t>
+          <t>50_FRST_AK_2</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -5374,16 +6764,21 @@
         </is>
       </c>
       <c r="C279">
-        <v>-157.40674</v>
+        <v>-148.46922222</v>
       </c>
       <c r="D279">
-        <v>70.47</v>
+        <v>70.16063889</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1543_FLXTWRZONA_SD_3</t>
+          <t>51_FRST_AK_2</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -5392,16 +6787,21 @@
         </is>
       </c>
       <c r="C280">
-        <v>-157.40674</v>
+        <v>-148.46891667</v>
       </c>
       <c r="D280">
-        <v>70.46925</v>
+        <v>70.16061111</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1544_FLXTWRZONA_SD_3</t>
+          <t>10_FRST_AK_3</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -5410,16 +6810,21 @@
         </is>
       </c>
       <c r="C281">
-        <v>-157.40922</v>
+        <v>-148.72047222</v>
       </c>
       <c r="D281">
-        <v>70.46935999999999</v>
+        <v>69.67397222</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1545_FLXTWRZONA_SD_3</t>
+          <t>11_FRST_AK_3</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -5428,16 +6833,21 @@
         </is>
       </c>
       <c r="C282">
-        <v>-157.41035</v>
+        <v>-148.7205</v>
       </c>
       <c r="D282">
-        <v>70.46804</v>
+        <v>69.67427778</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1546_FLXTWRZONA_SD_3</t>
+          <t>12_FRST_AK_3</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -5446,16 +6856,21 @@
         </is>
       </c>
       <c r="C283">
-        <v>-157.41096</v>
+        <v>-148.72055556</v>
       </c>
       <c r="D283">
-        <v>70.46957999999999</v>
+        <v>69.67444444</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1547_FLXTWRZONA_SD_3</t>
+          <t>13_FRST_AK_3</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -5464,16 +6879,21 @@
         </is>
       </c>
       <c r="C284">
-        <v>-157.41435</v>
+        <v>-148.72083333</v>
       </c>
       <c r="D284">
-        <v>70.46939999999999</v>
+        <v>69.67472222000001</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1548_FLXTWRZONA_SD_3</t>
+          <t>14_FRST_AK_3</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -5482,16 +6902,21 @@
         </is>
       </c>
       <c r="C285">
-        <v>-157.4092</v>
+        <v>-148.71716667</v>
       </c>
       <c r="D285">
-        <v>70.46974</v>
+        <v>69.67386111</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1549_FLXTWRZONA_SD_3</t>
+          <t>15_FRST_AK_3</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -5500,16 +6925,21 @@
         </is>
       </c>
       <c r="C286">
-        <v>-157.40997</v>
+        <v>-148.71733333</v>
       </c>
       <c r="D286">
-        <v>70.47049</v>
+        <v>69.67419443999999</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1550_FLXTWRZONA_SD_3</t>
+          <t>17_FRST_AK_3</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -5518,16 +6948,21 @@
         </is>
       </c>
       <c r="C287">
-        <v>-157.40912</v>
+        <v>-148.71875</v>
       </c>
       <c r="D287">
-        <v>70.46981</v>
+        <v>69.67397222</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1551_FLXTWRZONA_SD_3</t>
+          <t>18_FRST_AK_3</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -5536,16 +6971,21 @@
         </is>
       </c>
       <c r="C288">
-        <v>-157.40842</v>
+        <v>-148.72172222</v>
       </c>
       <c r="D288">
-        <v>70.47087000000001</v>
+        <v>69.67455556</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1552_FLXTWRZONA_SD_3</t>
+          <t>19_FRST_AK_3</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -5554,16 +6994,21 @@
         </is>
       </c>
       <c r="C289">
-        <v>-157.4056</v>
+        <v>-148.72152778</v>
       </c>
       <c r="D289">
-        <v>70.47022</v>
+        <v>69.67477778</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1553_FLXTWRZONA_SD_3</t>
+          <t>1_FRST_AK_3</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -5572,16 +7017,21 @@
         </is>
       </c>
       <c r="C290">
-        <v>-157.40839</v>
+        <v>-148.71622222</v>
       </c>
       <c r="D290">
-        <v>70.46944999999999</v>
+        <v>69.67408333</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1554_FLXTWRZONA_SD_3</t>
+          <t>20_FRST_AK_3</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -5590,16 +7040,21 @@
         </is>
       </c>
       <c r="C291">
-        <v>-157.40946</v>
+        <v>-148.72172222</v>
       </c>
       <c r="D291">
-        <v>70.46872</v>
+        <v>69.67486110999999</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1555_FLXTWRZONA_SD_3</t>
+          <t>2_FRST_AK_3</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -5608,16 +7063,21 @@
         </is>
       </c>
       <c r="C292">
-        <v>-157.41046</v>
+        <v>-148.71716667</v>
       </c>
       <c r="D292">
-        <v>70.46796000000001</v>
+        <v>69.67386111</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1556_FLXTWRZONA_SD_3</t>
+          <t>3_FRST_AK_3</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -5626,16 +7086,21 @@
         </is>
       </c>
       <c r="C293">
-        <v>-157.41001</v>
+        <v>-148.71733333</v>
       </c>
       <c r="D293">
-        <v>70.4696</v>
+        <v>69.67419443999999</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1557_FLXTWRZONA_SD_3</t>
+          <t>4_FRST_AK_3</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -5644,16 +7109,21 @@
         </is>
       </c>
       <c r="C294">
-        <v>-157.41318</v>
+        <v>-148.71875</v>
       </c>
       <c r="D294">
-        <v>70.46944999999999</v>
+        <v>69.67397222</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1558_FLXTWRZONA_SD_3</t>
+          <t>5_FRST_AK_3</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -5662,16 +7132,21 @@
         </is>
       </c>
       <c r="C295">
-        <v>-157.40967</v>
+        <v>-148.72027778</v>
       </c>
       <c r="D295">
-        <v>70.4701</v>
+        <v>69.67444444</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1559_FLXTWRZONA_SD_3</t>
+          <t>6_FRST_AK_3</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -5680,16 +7155,21 @@
         </is>
       </c>
       <c r="C296">
-        <v>-157.41052</v>
+        <v>-148.72111111</v>
       </c>
       <c r="D296">
-        <v>70.47136999999999</v>
+        <v>69.67472222000001</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1560_FLXTWRZONA_SD_3</t>
+          <t>7_FRST_AK_3</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -5698,574 +7178,734 @@
         </is>
       </c>
       <c r="C297">
-        <v>-157.40892</v>
+        <v>-148.72111111</v>
       </c>
       <c r="D297">
-        <v>70.47064</v>
+        <v>69.675</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1561_FLXTWRZONA_SD_3</t>
+          <t>8_FRST_AK_3</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C298">
-        <v>-157.40873</v>
+        <v>-148.72052778</v>
       </c>
       <c r="D298">
-        <v>70.47162</v>
+        <v>69.67430555999999</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1562_FLXTWRZONA_SD_4</t>
+          <t>9_FRST_AK_3</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C299">
-        <v>-155.7532</v>
+        <v>-148.72052778</v>
       </c>
       <c r="D299">
-        <v>68.48812</v>
+        <v>69.67427778</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1563_FLXTWRZONA_SD_4</t>
+          <t>1592_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C300">
-        <v>-155.75265</v>
+        <v>-148.423597</v>
       </c>
       <c r="D300">
-        <v>68.48835</v>
+        <v>70.196715</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1564_FLXTWRZONA_SD_4</t>
+          <t>1593_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C301">
-        <v>-155.75198</v>
+        <v>-148.423784</v>
       </c>
       <c r="D301">
-        <v>68.48863</v>
+        <v>70.196668</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1565_FLXTWRZONA_SD_4</t>
+          <t>1594_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C302">
-        <v>-155.75139</v>
+        <v>-148.423744</v>
       </c>
       <c r="D302">
-        <v>68.48887000000001</v>
+        <v>70.196612</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1566_FLXTWRZONA_SD_4</t>
+          <t>1596_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C303">
-        <v>-155.75079</v>
+        <v>-148.423577</v>
       </c>
       <c r="D303">
-        <v>68.48911</v>
+        <v>70.196499</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1567_FLXTWRZONA_SD_4</t>
+          <t>1597_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C304">
-        <v>-155.75208</v>
+        <v>-148.423446</v>
       </c>
       <c r="D304">
-        <v>68.48912</v>
+        <v>70.196513</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1568_FLXTWRZONA_SD_4</t>
+          <t>1598_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C305">
-        <v>-155.75279</v>
+        <v>-148.422913</v>
       </c>
       <c r="D305">
-        <v>68.48885</v>
+        <v>70.196364</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1569_FLXTWRZONA_SD_4</t>
+          <t>1599_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C306">
-        <v>-155.75322</v>
+        <v>-148.423128</v>
       </c>
       <c r="D306">
-        <v>68.48865000000001</v>
+        <v>70.196326</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1570_FLXTWRZONA_SD_4</t>
+          <t>1600_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C307">
-        <v>-155.75381</v>
+        <v>-148.422212</v>
       </c>
       <c r="D307">
-        <v>68.48845</v>
+        <v>70.196006</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1571_FLXTWRZONA_SD_4</t>
+          <t>1601_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C308">
-        <v>-155.75447</v>
+        <v>-148.422128</v>
       </c>
       <c r="D308">
-        <v>68.48829000000001</v>
+        <v>70.19605199999999</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1572_FLXTWRZONA_SD_4</t>
+          <t>1602_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C309">
-        <v>-155.75002</v>
+        <v>-148.4246471</v>
       </c>
       <c r="D309">
-        <v>68.4867</v>
+        <v>70.196764</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1573_FLXTWRZONA_SD_4</t>
+          <t>1603_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C310">
-        <v>-155.7487</v>
+        <v>-148.424562</v>
       </c>
       <c r="D310">
-        <v>68.48675</v>
+        <v>70.196776</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1574_FLXTWRZONA_SD_4</t>
+          <t>1604_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C311">
-        <v>-155.74717</v>
+        <v>-148.42461</v>
       </c>
       <c r="D311">
-        <v>68.4859</v>
+        <v>70.196839</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1575_FLXTWRZONA_SD_4</t>
+          <t>1606_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C312">
-        <v>-155.74916</v>
+        <v>-148.424911</v>
       </c>
       <c r="D312">
-        <v>68.48589</v>
+        <v>70.19690300000001</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1576_FLXTWRZONA_SD_4</t>
+          <t>1607_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C313">
-        <v>-155.75182</v>
+        <v>-148.42501</v>
       </c>
       <c r="D313">
-        <v>68.48565000000001</v>
+        <v>70.196861</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1577_FLXTWRZONA_SD_4</t>
+          <t>1608_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C314">
-        <v>-155.74873</v>
+        <v>-148.425259</v>
       </c>
       <c r="D314">
-        <v>68.4883</v>
+        <v>70.197047</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1578_FLXTWRZONA_SD_4</t>
+          <t>1609_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C315">
-        <v>-155.74864</v>
+        <v>-148.425555</v>
       </c>
       <c r="D315">
-        <v>68.48839</v>
+        <v>70.197047</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1579_FLXTWRZONA_SD_4</t>
+          <t>1610_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C316">
-        <v>-155.74856</v>
+        <v>-148.426283</v>
       </c>
       <c r="D316">
-        <v>68.48851999999999</v>
+        <v>70.19744900000001</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1580_FLXTWRZONA_SD_4</t>
+          <t>1611_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C317">
-        <v>-155.74834</v>
+        <v>-148.42623</v>
       </c>
       <c r="D317">
-        <v>68.48878000000001</v>
+        <v>70.197399</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1581_FLXTWRZONA_SD_4</t>
+          <t>1612_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C318">
-        <v>-155.74825</v>
+        <v>-148.426809</v>
       </c>
       <c r="D318">
-        <v>68.48887000000001</v>
+        <v>70.19577</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1582_FLXTWRZONA_SD_4</t>
+          <t>1613_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C319">
-        <v>-155.7486</v>
+        <v>-148.427013</v>
       </c>
       <c r="D319">
-        <v>68.48896999999999</v>
+        <v>70.195747</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1583_FLXTWRZONA_SD_4</t>
+          <t>1614_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C320">
-        <v>-155.74891</v>
+        <v>-148.427514</v>
       </c>
       <c r="D320">
-        <v>68.4889</v>
+        <v>70.195911</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1584_FLXTWRZONA_SD_4</t>
+          <t>1615_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C321">
-        <v>-155.74924</v>
+        <v>-148.427642</v>
       </c>
       <c r="D321">
-        <v>68.48873</v>
+        <v>70.195829</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1585_FLXTWRZONA_SD_4</t>
+          <t>1616_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C322">
-        <v>-155.74896</v>
+        <v>-148.427642</v>
       </c>
       <c r="D322">
-        <v>68.48855</v>
+        <v>70.195829</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1586_FLXTWRZONA_SD_4</t>
+          <t>1617_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C323">
-        <v>-155.74897</v>
+        <v>-148.428575</v>
       </c>
       <c r="D323">
-        <v>68.4885</v>
+        <v>70.196074</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1587_FLXTWRZONA_SD_4</t>
+          <t>1618_PRUAIR_DW_1</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C324">
-        <v>-155.7492</v>
+        <v>-148.428483</v>
       </c>
       <c r="D324">
-        <v>68.48753000000001</v>
+        <v>70.196016</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1588_FLXTWRZONA_SD_4</t>
+          <t>1413_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C325">
-        <v>-155.74678</v>
+        <v>-148.47140805</v>
       </c>
       <c r="D325">
-        <v>68.48724</v>
+        <v>70.22317916</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1589_FLXTWRZONA_SD_4</t>
+          <t>1414_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C326">
-        <v>-155.74938</v>
+        <v>-148.4716756</v>
       </c>
       <c r="D326">
-        <v>68.48638</v>
+        <v>70.22321881000001</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1590_FLXTWRZONA_SD_4</t>
+          <t>1415_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C327">
-        <v>-155.74812</v>
+        <v>-148.4713593</v>
       </c>
       <c r="D327">
-        <v>68.48508</v>
+        <v>70.22322543999999</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1591_FLXTWRZONA_SD_4</t>
+          <t>1416_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C328">
-        <v>-155.75168</v>
+        <v>-148.47172629</v>
       </c>
       <c r="D328">
-        <v>68.48714</v>
+        <v>70.22329396000001</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1592_PRUAIR_DW_1</t>
+          <t>1417_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -6274,16 +7914,21 @@
         </is>
       </c>
       <c r="C329">
-        <v>-148.423597</v>
+        <v>-148.47109754</v>
       </c>
       <c r="D329">
-        <v>70.196715</v>
+        <v>70.22333270999999</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1593_PRUAIR_DW_1</t>
+          <t>1418_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -6292,16 +7937,21 @@
         </is>
       </c>
       <c r="C330">
-        <v>-148.423784</v>
+        <v>-148.47151315</v>
       </c>
       <c r="D330">
-        <v>70.196668</v>
+        <v>70.22337813</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1594_PRUAIR_DW_1</t>
+          <t>1419_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -6310,16 +7960,21 @@
         </is>
       </c>
       <c r="C331">
-        <v>-148.423744</v>
+        <v>-148.47095379</v>
       </c>
       <c r="D331">
-        <v>70.196612</v>
+        <v>70.22356864</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1595_PRUAIR_DW_1</t>
+          <t>1420_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -6328,16 +7983,21 @@
         </is>
       </c>
       <c r="C332">
-        <v>-148.423458</v>
+        <v>-148.47124487</v>
       </c>
       <c r="D332">
-        <v>70.196645</v>
+        <v>70.22360955000001</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1596_PRUAIR_DW_1</t>
+          <t>1421_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -6346,16 +8006,21 @@
         </is>
       </c>
       <c r="C333">
-        <v>-148.423577</v>
+        <v>-148.47024093</v>
       </c>
       <c r="D333">
-        <v>70.196499</v>
+        <v>70.22394567000001</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1597_PRUAIR_DW_1</t>
+          <t>1422_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -6364,16 +8029,21 @@
         </is>
       </c>
       <c r="C334">
-        <v>-148.423446</v>
+        <v>-148.47028424</v>
       </c>
       <c r="D334">
-        <v>70.196513</v>
+        <v>70.22399661</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1598_PRUAIR_DW_1</t>
+          <t>1423_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -6382,16 +8052,21 @@
         </is>
       </c>
       <c r="C335">
-        <v>-148.422913</v>
+        <v>-148.4691739</v>
       </c>
       <c r="D335">
-        <v>70.196364</v>
+        <v>70.22478794</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1599_PRUAIR_DW_1</t>
+          <t>1424_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -6400,16 +8075,21 @@
         </is>
       </c>
       <c r="C336">
-        <v>-148.423128</v>
+        <v>-148.46932532</v>
       </c>
       <c r="D336">
-        <v>70.196326</v>
+        <v>70.22478943</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1600_PRUAIR_DW_1</t>
+          <t>1425_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -6418,16 +8098,21 @@
         </is>
       </c>
       <c r="C337">
-        <v>-148.422212</v>
+        <v>-148.47125808</v>
       </c>
       <c r="D337">
-        <v>70.196006</v>
+        <v>70.22291749999999</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1601_PRUAIR_DW_1</t>
+          <t>1426_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -6436,16 +8121,21 @@
         </is>
       </c>
       <c r="C338">
-        <v>-148.422128</v>
+        <v>-148.47091</v>
       </c>
       <c r="D338">
-        <v>70.19605199999999</v>
+        <v>70.22287111999999</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1602_PRUAIR_DW_1</t>
+          <t>1427_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -6454,16 +8144,21 @@
         </is>
       </c>
       <c r="C339">
-        <v>-148.4246471</v>
+        <v>-148.47125468</v>
       </c>
       <c r="D339">
-        <v>70.196764</v>
+        <v>70.22287787</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1603_PRUAIR_DW_1</t>
+          <t>1428_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -6472,16 +8167,21 @@
         </is>
       </c>
       <c r="C340">
-        <v>-148.424562</v>
+        <v>-148.47143883</v>
       </c>
       <c r="D340">
-        <v>70.196776</v>
+        <v>70.22289397999999</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1604_PRUAIR_DW_1</t>
+          <t>1429_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -6490,16 +8190,21 @@
         </is>
       </c>
       <c r="C341">
-        <v>-148.42461</v>
+        <v>-148.47148563</v>
       </c>
       <c r="D341">
-        <v>70.196839</v>
+        <v>70.22277081</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1605_PRUAIR_DW_1</t>
+          <t>1430_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -6508,16 +8213,21 @@
         </is>
       </c>
       <c r="C342">
-        <v>-148.424725</v>
+        <v>-148.47163501</v>
       </c>
       <c r="D342">
-        <v>70.19681</v>
+        <v>70.22277261000001</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1606_PRUAIR_DW_1</t>
+          <t>1431_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -6526,16 +8236,21 @@
         </is>
       </c>
       <c r="C343">
-        <v>-148.424911</v>
+        <v>-148.47176882</v>
       </c>
       <c r="D343">
-        <v>70.19690300000001</v>
+        <v>70.22259928</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1607_PRUAIR_DW_1</t>
+          <t>1432_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -6544,16 +8259,21 @@
         </is>
       </c>
       <c r="C344">
-        <v>-148.42501</v>
+        <v>-148.47197271</v>
       </c>
       <c r="D344">
-        <v>70.196861</v>
+        <v>70.22258632</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1608_PRUAIR_DW_1</t>
+          <t>1433_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -6562,16 +8282,21 @@
         </is>
       </c>
       <c r="C345">
-        <v>-148.425259</v>
+        <v>-148.47251118</v>
       </c>
       <c r="D345">
-        <v>70.197047</v>
+        <v>70.22215088999999</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1609_PRUAIR_DW_1</t>
+          <t>1434_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -6580,16 +8305,21 @@
         </is>
       </c>
       <c r="C346">
-        <v>-148.425555</v>
+        <v>-148.4724173</v>
       </c>
       <c r="D346">
-        <v>70.197047</v>
+        <v>70.2220621</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1610_PRUAIR_DW_1</t>
+          <t>1435_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -6598,16 +8328,21 @@
         </is>
       </c>
       <c r="C347">
-        <v>-148.426283</v>
+        <v>-148.47353697</v>
       </c>
       <c r="D347">
-        <v>70.19744900000001</v>
+        <v>70.22136116999999</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1611_PRUAIR_DW_1</t>
+          <t>1436_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -6616,16 +8351,21 @@
         </is>
       </c>
       <c r="C348">
-        <v>-148.42623</v>
+        <v>-148.47367271</v>
       </c>
       <c r="D348">
-        <v>70.197399</v>
+        <v>70.22136857</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1612_PRUAIR_DW_1</t>
+          <t>1437_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -6634,16 +8374,21 @@
         </is>
       </c>
       <c r="C349">
-        <v>-148.426809</v>
+        <v>-148.4714481</v>
       </c>
       <c r="D349">
-        <v>70.19577</v>
+        <v>70.22315542</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1613_PRUAIR_DW_1</t>
+          <t>1438_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -6652,16 +8397,21 @@
         </is>
       </c>
       <c r="C350">
-        <v>-148.427013</v>
+        <v>-148.46774151</v>
       </c>
       <c r="D350">
-        <v>70.195747</v>
+        <v>70.2224595</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1614_PRUAIR_DW_1</t>
+          <t>1439_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -6670,16 +8420,21 @@
         </is>
       </c>
       <c r="C351">
-        <v>-148.427514</v>
+        <v>-148.46782079</v>
       </c>
       <c r="D351">
-        <v>70.195911</v>
+        <v>70.22243082999999</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1615_PRUAIR_DW_1</t>
+          <t>1440_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -6688,16 +8443,21 @@
         </is>
       </c>
       <c r="C352">
-        <v>-148.427642</v>
+        <v>-148.46585804</v>
       </c>
       <c r="D352">
-        <v>70.195829</v>
+        <v>70.22689676</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1616_PRUAIR_DW_1</t>
+          <t>1441_PRUARC_DW_1</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -6706,46 +8466,15 @@
         </is>
       </c>
       <c r="C353">
-        <v>-148.427642</v>
+        <v>-148.46728725</v>
       </c>
       <c r="D353">
-        <v>70.195829</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>1617_PRUAIR_DW_1</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C354">
-        <v>-148.428575</v>
-      </c>
-      <c r="D354">
-        <v>70.196074</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>1618_PRUAIR_DW_1</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C355">
-        <v>-148.428483</v>
-      </c>
-      <c r="D355">
-        <v>70.196016</v>
+        <v>70.22610928</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
   </sheetData>
